--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="266">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -568,6 +568,9 @@
     <t>['19', '29']</t>
   </si>
   <si>
+    <t>['19']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -746,9 +749,6 @@
   </si>
   <si>
     <t>['65']</t>
-  </si>
-  <si>
-    <t>['19']</t>
   </si>
   <si>
     <t>['2', '18', '22', '73', '89']</t>
@@ -1173,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1429,7 +1429,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1635,7 +1635,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1716,7 +1716,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5">
         <v>1.63</v>
@@ -2253,7 +2253,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2459,7 +2459,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2871,7 +2871,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2952,7 +2952,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ10">
         <v>1.13</v>
@@ -3283,7 +3283,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3695,7 +3695,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3901,7 +3901,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4107,7 +4107,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4313,7 +4313,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4931,7 +4931,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5137,7 +5137,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5421,7 +5421,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ21">
         <v>0.88</v>
@@ -5755,7 +5755,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5836,7 +5836,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -6039,7 +6039,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
         <v>0.33</v>
@@ -6167,7 +6167,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6579,7 +6579,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6866,7 +6866,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR28">
         <v>1.62</v>
@@ -6991,7 +6991,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7197,7 +7197,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7609,7 +7609,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8021,7 +8021,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8227,7 +8227,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8433,7 +8433,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8845,7 +8845,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9051,7 +9051,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9129,7 +9129,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ39">
         <v>1.63</v>
@@ -9335,7 +9335,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ40">
         <v>1.78</v>
@@ -9463,7 +9463,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9669,7 +9669,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10081,7 +10081,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10287,7 +10287,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10368,7 +10368,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ45">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR45">
         <v>1.58</v>
@@ -10574,7 +10574,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ46">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR46">
         <v>1.7</v>
@@ -10699,7 +10699,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10905,7 +10905,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11111,7 +11111,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11317,7 +11317,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11523,7 +11523,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12141,7 +12141,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12553,7 +12553,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12759,7 +12759,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -12837,7 +12837,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -13171,7 +13171,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13252,7 +13252,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ59">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.13</v>
@@ -13664,7 +13664,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ61">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR61">
         <v>1.62</v>
@@ -14407,7 +14407,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14819,7 +14819,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15025,7 +15025,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15103,7 +15103,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ68">
         <v>1.44</v>
@@ -15930,7 +15930,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ72">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR72">
         <v>1.62</v>
@@ -16055,7 +16055,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16261,7 +16261,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16467,7 +16467,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16673,7 +16673,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17085,7 +17085,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17163,7 +17163,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ78">
         <v>1.44</v>
@@ -17497,7 +17497,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17990,7 +17990,7 @@
         <v>1</v>
       </c>
       <c r="AQ82">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR82">
         <v>1.36</v>
@@ -18115,7 +18115,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18402,7 +18402,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18605,7 +18605,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ85">
         <v>1.5</v>
@@ -18733,7 +18733,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -18811,7 +18811,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ86">
         <v>0.75</v>
@@ -19145,7 +19145,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19557,7 +19557,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19763,7 +19763,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -19969,7 +19969,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20175,7 +20175,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20381,7 +20381,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20587,7 +20587,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20999,7 +20999,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21205,7 +21205,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21411,7 +21411,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22107,7 +22107,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ102">
         <v>0.63</v>
@@ -22235,7 +22235,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22313,7 +22313,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ103">
         <v>1.43</v>
@@ -22647,7 +22647,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22853,7 +22853,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -22934,7 +22934,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ106">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR106">
         <v>1.65</v>
@@ -23059,7 +23059,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23265,7 +23265,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23346,7 +23346,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ108">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR108">
         <v>1.57</v>
@@ -23471,7 +23471,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23677,7 +23677,7 @@
         <v>117</v>
       </c>
       <c r="P110" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="Q110">
         <v>2.56</v>
@@ -25818,7 +25818,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ120">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR120">
         <v>1.47</v>
@@ -26639,10 +26639,10 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ124">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR124">
         <v>1.69</v>
@@ -27463,7 +27463,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ128">
         <v>0.63</v>
@@ -31662,6 +31662,418 @@
       </c>
       <c r="BP148">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7502746</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45669.33333333334</v>
+      </c>
+      <c r="F149">
+        <v>16</v>
+      </c>
+      <c r="G149" t="s">
+        <v>73</v>
+      </c>
+      <c r="H149" t="s">
+        <v>84</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149" t="s">
+        <v>89</v>
+      </c>
+      <c r="P149" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q149">
+        <v>3.05</v>
+      </c>
+      <c r="R149">
+        <v>2.02</v>
+      </c>
+      <c r="S149">
+        <v>3.54</v>
+      </c>
+      <c r="T149">
+        <v>1.46</v>
+      </c>
+      <c r="U149">
+        <v>2.6</v>
+      </c>
+      <c r="V149">
+        <v>3.14</v>
+      </c>
+      <c r="W149">
+        <v>1.33</v>
+      </c>
+      <c r="X149">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y149">
+        <v>1.06</v>
+      </c>
+      <c r="Z149">
+        <v>2.35</v>
+      </c>
+      <c r="AA149">
+        <v>3.1</v>
+      </c>
+      <c r="AB149">
+        <v>2.7</v>
+      </c>
+      <c r="AC149">
+        <v>1.03</v>
+      </c>
+      <c r="AD149">
+        <v>7.5</v>
+      </c>
+      <c r="AE149">
+        <v>1.33</v>
+      </c>
+      <c r="AF149">
+        <v>2.82</v>
+      </c>
+      <c r="AG149">
+        <v>2.1</v>
+      </c>
+      <c r="AH149">
+        <v>1.65</v>
+      </c>
+      <c r="AI149">
+        <v>1.85</v>
+      </c>
+      <c r="AJ149">
+        <v>1.85</v>
+      </c>
+      <c r="AK149">
+        <v>1.4</v>
+      </c>
+      <c r="AL149">
+        <v>1.32</v>
+      </c>
+      <c r="AM149">
+        <v>1.52</v>
+      </c>
+      <c r="AN149">
+        <v>1.86</v>
+      </c>
+      <c r="AO149">
+        <v>1.13</v>
+      </c>
+      <c r="AP149">
+        <v>1.75</v>
+      </c>
+      <c r="AQ149">
+        <v>1.11</v>
+      </c>
+      <c r="AR149">
+        <v>1.55</v>
+      </c>
+      <c r="AS149">
+        <v>1.25</v>
+      </c>
+      <c r="AT149">
+        <v>2.8</v>
+      </c>
+      <c r="AU149">
+        <v>5</v>
+      </c>
+      <c r="AV149">
+        <v>5</v>
+      </c>
+      <c r="AW149">
+        <v>2</v>
+      </c>
+      <c r="AX149">
+        <v>15</v>
+      </c>
+      <c r="AY149">
+        <v>7</v>
+      </c>
+      <c r="AZ149">
+        <v>20</v>
+      </c>
+      <c r="BA149">
+        <v>-1</v>
+      </c>
+      <c r="BB149">
+        <v>-1</v>
+      </c>
+      <c r="BC149">
+        <v>-1</v>
+      </c>
+      <c r="BD149">
+        <v>1.95</v>
+      </c>
+      <c r="BE149">
+        <v>7</v>
+      </c>
+      <c r="BF149">
+        <v>2.22</v>
+      </c>
+      <c r="BG149">
+        <v>1.15</v>
+      </c>
+      <c r="BH149">
+        <v>4.3</v>
+      </c>
+      <c r="BI149">
+        <v>1.31</v>
+      </c>
+      <c r="BJ149">
+        <v>2.92</v>
+      </c>
+      <c r="BK149">
+        <v>1.58</v>
+      </c>
+      <c r="BL149">
+        <v>2.17</v>
+      </c>
+      <c r="BM149">
+        <v>1.99</v>
+      </c>
+      <c r="BN149">
+        <v>1.73</v>
+      </c>
+      <c r="BO149">
+        <v>2.57</v>
+      </c>
+      <c r="BP149">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7502747</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45669.33333333334</v>
+      </c>
+      <c r="F150">
+        <v>16</v>
+      </c>
+      <c r="G150" t="s">
+        <v>78</v>
+      </c>
+      <c r="H150" t="s">
+        <v>82</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>184</v>
+      </c>
+      <c r="P150" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q150">
+        <v>2.57</v>
+      </c>
+      <c r="R150">
+        <v>2.05</v>
+      </c>
+      <c r="S150">
+        <v>4.4</v>
+      </c>
+      <c r="T150">
+        <v>1.44</v>
+      </c>
+      <c r="U150">
+        <v>2.67</v>
+      </c>
+      <c r="V150">
+        <v>3.1</v>
+      </c>
+      <c r="W150">
+        <v>1.34</v>
+      </c>
+      <c r="X150">
+        <v>8.4</v>
+      </c>
+      <c r="Y150">
+        <v>1.05</v>
+      </c>
+      <c r="Z150">
+        <v>1.91</v>
+      </c>
+      <c r="AA150">
+        <v>3.25</v>
+      </c>
+      <c r="AB150">
+        <v>3.45</v>
+      </c>
+      <c r="AC150">
+        <v>1.01</v>
+      </c>
+      <c r="AD150">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE150">
+        <v>1.31</v>
+      </c>
+      <c r="AF150">
+        <v>2.93</v>
+      </c>
+      <c r="AG150">
+        <v>2</v>
+      </c>
+      <c r="AH150">
+        <v>1.7</v>
+      </c>
+      <c r="AI150">
+        <v>1.87</v>
+      </c>
+      <c r="AJ150">
+        <v>1.83</v>
+      </c>
+      <c r="AK150">
+        <v>1.25</v>
+      </c>
+      <c r="AL150">
+        <v>1.29</v>
+      </c>
+      <c r="AM150">
+        <v>1.79</v>
+      </c>
+      <c r="AN150">
+        <v>0.88</v>
+      </c>
+      <c r="AO150">
+        <v>1.43</v>
+      </c>
+      <c r="AP150">
+        <v>1.11</v>
+      </c>
+      <c r="AQ150">
+        <v>1.25</v>
+      </c>
+      <c r="AR150">
+        <v>1.63</v>
+      </c>
+      <c r="AS150">
+        <v>1.21</v>
+      </c>
+      <c r="AT150">
+        <v>2.84</v>
+      </c>
+      <c r="AU150">
+        <v>5</v>
+      </c>
+      <c r="AV150">
+        <v>3</v>
+      </c>
+      <c r="AW150">
+        <v>6</v>
+      </c>
+      <c r="AX150">
+        <v>10</v>
+      </c>
+      <c r="AY150">
+        <v>11</v>
+      </c>
+      <c r="AZ150">
+        <v>13</v>
+      </c>
+      <c r="BA150">
+        <v>-1</v>
+      </c>
+      <c r="BB150">
+        <v>-1</v>
+      </c>
+      <c r="BC150">
+        <v>-1</v>
+      </c>
+      <c r="BD150">
+        <v>1.5</v>
+      </c>
+      <c r="BE150">
+        <v>8.9</v>
+      </c>
+      <c r="BF150">
+        <v>3.06</v>
+      </c>
+      <c r="BG150">
+        <v>1.14</v>
+      </c>
+      <c r="BH150">
+        <v>4.45</v>
+      </c>
+      <c r="BI150">
+        <v>1.29</v>
+      </c>
+      <c r="BJ150">
+        <v>3.04</v>
+      </c>
+      <c r="BK150">
+        <v>1.54</v>
+      </c>
+      <c r="BL150">
+        <v>2.25</v>
+      </c>
+      <c r="BM150">
+        <v>1.92</v>
+      </c>
+      <c r="BN150">
+        <v>1.79</v>
+      </c>
+      <c r="BO150">
+        <v>2.45</v>
+      </c>
+      <c r="BP150">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="271">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,12 @@
     <t>['19']</t>
   </si>
   <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['90+6']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -812,6 +818,15 @@
   </si>
   <si>
     <t>['53']</t>
+  </si>
+  <si>
+    <t>['12', '68']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1429,7 +1444,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1510,7 +1525,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ2">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1635,7 +1650,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1841,7 +1856,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -1919,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>1.5</v>
@@ -2128,7 +2143,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ5">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2253,7 +2268,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2459,7 +2474,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2743,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -2871,7 +2886,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -2949,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9">
         <v>1.11</v>
@@ -3158,7 +3173,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ10">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3283,7 +3298,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3361,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ11">
         <v>1.5</v>
@@ -3695,7 +3710,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3901,7 +3916,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4107,7 +4122,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4313,7 +4328,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4806,7 +4821,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ18">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4931,7 +4946,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5137,7 +5152,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5215,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ20">
         <v>1.33</v>
@@ -5755,7 +5770,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5833,7 +5848,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>1.25</v>
@@ -6167,7 +6182,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6248,7 +6263,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ25">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR25">
         <v>1.23</v>
@@ -6454,7 +6469,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ26">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR26">
         <v>1.66</v>
@@ -6579,7 +6594,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6660,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR27">
         <v>1.33</v>
@@ -6991,7 +7006,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7069,7 +7084,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -7197,7 +7212,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7609,7 +7624,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7690,7 +7705,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ32">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR32">
         <v>2.27</v>
@@ -8021,7 +8036,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8227,7 +8242,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8433,7 +8448,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8717,7 +8732,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>1.78</v>
@@ -8845,7 +8860,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -8926,7 +8941,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>1.5</v>
@@ -9051,7 +9066,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9132,7 +9147,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ39">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR39">
         <v>1.92</v>
@@ -9463,7 +9478,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9669,7 +9684,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9750,7 +9765,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR42">
         <v>1.42</v>
@@ -10081,7 +10096,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10287,7 +10302,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10365,7 +10380,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1.11</v>
@@ -10699,7 +10714,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10780,7 +10795,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR47">
         <v>1.36</v>
@@ -10905,7 +10920,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11111,7 +11126,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11317,7 +11332,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11523,7 +11538,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11601,7 +11616,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
         <v>1.5</v>
@@ -12013,7 +12028,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ53">
         <v>0.63</v>
@@ -12141,7 +12156,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12219,7 +12234,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ54">
         <v>1.44</v>
@@ -12553,7 +12568,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12634,7 +12649,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -12759,7 +12774,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13171,7 +13186,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13455,10 +13470,10 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -14282,7 +14297,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ64">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR64">
         <v>1.67</v>
@@ -14407,7 +14422,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14485,7 +14500,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ65">
         <v>1.5</v>
@@ -14819,7 +14834,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -14897,7 +14912,7 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ67">
         <v>2.38</v>
@@ -15025,7 +15040,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15312,7 +15327,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ69">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR69">
         <v>1.69</v>
@@ -15721,7 +15736,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ71">
         <v>0.75</v>
@@ -16055,7 +16070,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16261,7 +16276,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16342,7 +16357,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ74">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR74">
         <v>1.25</v>
@@ -16467,7 +16482,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16548,7 +16563,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ75">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR75">
         <v>1.62</v>
@@ -16673,7 +16688,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -16754,7 +16769,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ76">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17085,7 +17100,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17369,7 +17384,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>0.33</v>
@@ -17497,7 +17512,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17781,7 +17796,7 @@
         <v>1.25</v>
       </c>
       <c r="AP81">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ81">
         <v>0.88</v>
@@ -18115,7 +18130,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18733,7 +18748,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19017,7 +19032,7 @@
         <v>1.25</v>
       </c>
       <c r="AP87">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ87">
         <v>0.63</v>
@@ -19145,7 +19160,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19223,10 +19238,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR88">
         <v>1.05</v>
@@ -19557,7 +19572,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19638,7 +19653,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ90">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19763,7 +19778,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -19969,7 +19984,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20050,7 +20065,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR92">
         <v>1.19</v>
@@ -20175,7 +20190,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20381,7 +20396,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20462,7 +20477,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ94">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR94">
         <v>1.74</v>
@@ -20587,7 +20602,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20871,7 +20886,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>1.44</v>
@@ -20999,7 +21014,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21205,7 +21220,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21411,7 +21426,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22235,7 +22250,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22316,7 +22331,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ103">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR103">
         <v>1.71</v>
@@ -22519,7 +22534,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ104">
         <v>0.88</v>
@@ -22647,7 +22662,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22728,7 +22743,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -22853,7 +22868,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -22931,7 +22946,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ106">
         <v>1.11</v>
@@ -23059,7 +23074,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23265,7 +23280,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23471,7 +23486,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23549,7 +23564,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ109">
         <v>0.63</v>
@@ -24295,7 +24310,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24501,7 +24516,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24579,7 +24594,7 @@
         <v>1.6</v>
       </c>
       <c r="AP114">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>1.5</v>
@@ -24788,7 +24803,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ115">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.59</v>
@@ -24913,7 +24928,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25119,7 +25134,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25325,7 +25340,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25612,7 +25627,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ119">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -25815,7 +25830,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ120">
         <v>1.25</v>
@@ -26021,10 +26036,10 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AQ121">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR121">
         <v>1.6</v>
@@ -26149,7 +26164,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26561,7 +26576,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26848,7 +26863,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ125">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR125">
         <v>1.63</v>
@@ -26973,7 +26988,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27054,7 +27069,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ126">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27257,7 +27272,7 @@
         <v>0.83</v>
       </c>
       <c r="AP127">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ127">
         <v>0.88</v>
@@ -27385,7 +27400,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27669,7 +27684,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ129">
         <v>0.75</v>
@@ -27797,7 +27812,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28209,7 +28224,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28290,7 +28305,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ132">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR132">
         <v>1.39</v>
@@ -28415,7 +28430,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28621,7 +28636,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29239,7 +29254,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29651,7 +29666,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30063,7 +30078,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30475,7 +30490,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30681,7 +30696,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31093,7 +31108,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31299,7 +31314,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31505,7 +31520,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31822,13 +31837,13 @@
         <v>20</v>
       </c>
       <c r="BA149">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB149">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BC149">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BD149">
         <v>1.95</v>
@@ -32010,31 +32025,31 @@
         <v>2.84</v>
       </c>
       <c r="AU150">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV150">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW150">
         <v>6</v>
       </c>
       <c r="AX150">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY150">
+        <v>8</v>
+      </c>
+      <c r="AZ150">
         <v>11</v>
       </c>
-      <c r="AZ150">
-        <v>13</v>
-      </c>
       <c r="BA150">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB150">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BC150">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD150">
         <v>1.5</v>
@@ -32074,6 +32089,830 @@
       </c>
       <c r="BP150">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7502744</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45669.40625</v>
+      </c>
+      <c r="F151">
+        <v>16</v>
+      </c>
+      <c r="G151" t="s">
+        <v>76</v>
+      </c>
+      <c r="H151" t="s">
+        <v>81</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>2</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="M151">
+        <v>2</v>
+      </c>
+      <c r="N151">
+        <v>3</v>
+      </c>
+      <c r="O151" t="s">
+        <v>129</v>
+      </c>
+      <c r="P151" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q151">
+        <v>2.78</v>
+      </c>
+      <c r="R151">
+        <v>2.11</v>
+      </c>
+      <c r="S151">
+        <v>3.68</v>
+      </c>
+      <c r="T151">
+        <v>1.39</v>
+      </c>
+      <c r="U151">
+        <v>2.86</v>
+      </c>
+      <c r="V151">
+        <v>2.82</v>
+      </c>
+      <c r="W151">
+        <v>1.4</v>
+      </c>
+      <c r="X151">
+        <v>7.2</v>
+      </c>
+      <c r="Y151">
+        <v>1.08</v>
+      </c>
+      <c r="Z151">
+        <v>2.25</v>
+      </c>
+      <c r="AA151">
+        <v>3.3</v>
+      </c>
+      <c r="AB151">
+        <v>3.1</v>
+      </c>
+      <c r="AC151">
+        <v>1.01</v>
+      </c>
+      <c r="AD151">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE151">
+        <v>1.26</v>
+      </c>
+      <c r="AF151">
+        <v>3.22</v>
+      </c>
+      <c r="AG151">
+        <v>1.98</v>
+      </c>
+      <c r="AH151">
+        <v>1.88</v>
+      </c>
+      <c r="AI151">
+        <v>1.73</v>
+      </c>
+      <c r="AJ151">
+        <v>1.99</v>
+      </c>
+      <c r="AK151">
+        <v>1.35</v>
+      </c>
+      <c r="AL151">
+        <v>1.29</v>
+      </c>
+      <c r="AM151">
+        <v>1.63</v>
+      </c>
+      <c r="AN151">
+        <v>1.43</v>
+      </c>
+      <c r="AO151">
+        <v>1.13</v>
+      </c>
+      <c r="AP151">
+        <v>1.25</v>
+      </c>
+      <c r="AQ151">
+        <v>1.33</v>
+      </c>
+      <c r="AR151">
+        <v>1.02</v>
+      </c>
+      <c r="AS151">
+        <v>1.16</v>
+      </c>
+      <c r="AT151">
+        <v>2.18</v>
+      </c>
+      <c r="AU151">
+        <v>2</v>
+      </c>
+      <c r="AV151">
+        <v>3</v>
+      </c>
+      <c r="AW151">
+        <v>6</v>
+      </c>
+      <c r="AX151">
+        <v>3</v>
+      </c>
+      <c r="AY151">
+        <v>8</v>
+      </c>
+      <c r="AZ151">
+        <v>6</v>
+      </c>
+      <c r="BA151">
+        <v>-1</v>
+      </c>
+      <c r="BB151">
+        <v>-1</v>
+      </c>
+      <c r="BC151">
+        <v>-1</v>
+      </c>
+      <c r="BD151">
+        <v>1.55</v>
+      </c>
+      <c r="BE151">
+        <v>8.6</v>
+      </c>
+      <c r="BF151">
+        <v>2.91</v>
+      </c>
+      <c r="BG151">
+        <v>1.15</v>
+      </c>
+      <c r="BH151">
+        <v>4.2</v>
+      </c>
+      <c r="BI151">
+        <v>1.32</v>
+      </c>
+      <c r="BJ151">
+        <v>2.88</v>
+      </c>
+      <c r="BK151">
+        <v>1.58</v>
+      </c>
+      <c r="BL151">
+        <v>2.17</v>
+      </c>
+      <c r="BM151">
+        <v>1.99</v>
+      </c>
+      <c r="BN151">
+        <v>1.73</v>
+      </c>
+      <c r="BO151">
+        <v>2.57</v>
+      </c>
+      <c r="BP151">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7502743</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45669.625</v>
+      </c>
+      <c r="F152">
+        <v>16</v>
+      </c>
+      <c r="G152" t="s">
+        <v>72</v>
+      </c>
+      <c r="H152" t="s">
+        <v>75</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152" t="s">
+        <v>185</v>
+      </c>
+      <c r="P152" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q152">
+        <v>2.81</v>
+      </c>
+      <c r="R152">
+        <v>1.97</v>
+      </c>
+      <c r="S152">
+        <v>4.15</v>
+      </c>
+      <c r="T152">
+        <v>1.52</v>
+      </c>
+      <c r="U152">
+        <v>2.43</v>
+      </c>
+      <c r="V152">
+        <v>3.34</v>
+      </c>
+      <c r="W152">
+        <v>1.3</v>
+      </c>
+      <c r="X152">
+        <v>8.4</v>
+      </c>
+      <c r="Y152">
+        <v>1.05</v>
+      </c>
+      <c r="Z152">
+        <v>2.2</v>
+      </c>
+      <c r="AA152">
+        <v>3</v>
+      </c>
+      <c r="AB152">
+        <v>3.3</v>
+      </c>
+      <c r="AC152">
+        <v>1.06</v>
+      </c>
+      <c r="AD152">
+        <v>6.1</v>
+      </c>
+      <c r="AE152">
+        <v>1.42</v>
+      </c>
+      <c r="AF152">
+        <v>2.5</v>
+      </c>
+      <c r="AG152">
+        <v>2.25</v>
+      </c>
+      <c r="AH152">
+        <v>1.53</v>
+      </c>
+      <c r="AI152">
+        <v>2</v>
+      </c>
+      <c r="AJ152">
+        <v>1.72</v>
+      </c>
+      <c r="AK152">
+        <v>1.3</v>
+      </c>
+      <c r="AL152">
+        <v>1.33</v>
+      </c>
+      <c r="AM152">
+        <v>1.64</v>
+      </c>
+      <c r="AN152">
+        <v>2.13</v>
+      </c>
+      <c r="AO152">
+        <v>1.43</v>
+      </c>
+      <c r="AP152">
+        <v>2</v>
+      </c>
+      <c r="AQ152">
+        <v>1.38</v>
+      </c>
+      <c r="AR152">
+        <v>1.34</v>
+      </c>
+      <c r="AS152">
+        <v>1.38</v>
+      </c>
+      <c r="AT152">
+        <v>2.72</v>
+      </c>
+      <c r="AU152">
+        <v>6</v>
+      </c>
+      <c r="AV152">
+        <v>3</v>
+      </c>
+      <c r="AW152">
+        <v>5</v>
+      </c>
+      <c r="AX152">
+        <v>6</v>
+      </c>
+      <c r="AY152">
+        <v>11</v>
+      </c>
+      <c r="AZ152">
+        <v>9</v>
+      </c>
+      <c r="BA152">
+        <v>8</v>
+      </c>
+      <c r="BB152">
+        <v>7</v>
+      </c>
+      <c r="BC152">
+        <v>15</v>
+      </c>
+      <c r="BD152">
+        <v>1.67</v>
+      </c>
+      <c r="BE152">
+        <v>8.4</v>
+      </c>
+      <c r="BF152">
+        <v>2.58</v>
+      </c>
+      <c r="BG152">
+        <v>1.18</v>
+      </c>
+      <c r="BH152">
+        <v>3.9</v>
+      </c>
+      <c r="BI152">
+        <v>1.37</v>
+      </c>
+      <c r="BJ152">
+        <v>2.75</v>
+      </c>
+      <c r="BK152">
+        <v>1.67</v>
+      </c>
+      <c r="BL152">
+        <v>2.07</v>
+      </c>
+      <c r="BM152">
+        <v>2.09</v>
+      </c>
+      <c r="BN152">
+        <v>1.63</v>
+      </c>
+      <c r="BO152">
+        <v>2.7</v>
+      </c>
+      <c r="BP152">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7502741</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45669.625</v>
+      </c>
+      <c r="F153">
+        <v>16</v>
+      </c>
+      <c r="G153" t="s">
+        <v>77</v>
+      </c>
+      <c r="H153" t="s">
+        <v>85</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <v>1</v>
+      </c>
+      <c r="N153">
+        <v>2</v>
+      </c>
+      <c r="O153" t="s">
+        <v>140</v>
+      </c>
+      <c r="P153" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q153">
+        <v>2.96</v>
+      </c>
+      <c r="R153">
+        <v>1.99</v>
+      </c>
+      <c r="S153">
+        <v>3.78</v>
+      </c>
+      <c r="T153">
+        <v>1.46</v>
+      </c>
+      <c r="U153">
+        <v>2.6</v>
+      </c>
+      <c r="V153">
+        <v>3.2</v>
+      </c>
+      <c r="W153">
+        <v>1.32</v>
+      </c>
+      <c r="X153">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y153">
+        <v>1.04</v>
+      </c>
+      <c r="Z153">
+        <v>2.4</v>
+      </c>
+      <c r="AA153">
+        <v>3</v>
+      </c>
+      <c r="AB153">
+        <v>3</v>
+      </c>
+      <c r="AC153">
+        <v>1.01</v>
+      </c>
+      <c r="AD153">
+        <v>8.4</v>
+      </c>
+      <c r="AE153">
+        <v>1.33</v>
+      </c>
+      <c r="AF153">
+        <v>2.82</v>
+      </c>
+      <c r="AG153">
+        <v>2.1</v>
+      </c>
+      <c r="AH153">
+        <v>1.6</v>
+      </c>
+      <c r="AI153">
+        <v>1.88</v>
+      </c>
+      <c r="AJ153">
+        <v>1.82</v>
+      </c>
+      <c r="AK153">
+        <v>1.35</v>
+      </c>
+      <c r="AL153">
+        <v>1.32</v>
+      </c>
+      <c r="AM153">
+        <v>1.58</v>
+      </c>
+      <c r="AN153">
+        <v>1.14</v>
+      </c>
+      <c r="AO153">
+        <v>1.63</v>
+      </c>
+      <c r="AP153">
+        <v>1.13</v>
+      </c>
+      <c r="AQ153">
+        <v>1.56</v>
+      </c>
+      <c r="AR153">
+        <v>1.48</v>
+      </c>
+      <c r="AS153">
+        <v>1.47</v>
+      </c>
+      <c r="AT153">
+        <v>2.95</v>
+      </c>
+      <c r="AU153">
+        <v>7</v>
+      </c>
+      <c r="AV153">
+        <v>6</v>
+      </c>
+      <c r="AW153">
+        <v>8</v>
+      </c>
+      <c r="AX153">
+        <v>7</v>
+      </c>
+      <c r="AY153">
+        <v>15</v>
+      </c>
+      <c r="AZ153">
+        <v>13</v>
+      </c>
+      <c r="BA153">
+        <v>3</v>
+      </c>
+      <c r="BB153">
+        <v>5</v>
+      </c>
+      <c r="BC153">
+        <v>8</v>
+      </c>
+      <c r="BD153">
+        <v>1.91</v>
+      </c>
+      <c r="BE153">
+        <v>7.1</v>
+      </c>
+      <c r="BF153">
+        <v>2.27</v>
+      </c>
+      <c r="BG153">
+        <v>1.14</v>
+      </c>
+      <c r="BH153">
+        <v>4.45</v>
+      </c>
+      <c r="BI153">
+        <v>1.29</v>
+      </c>
+      <c r="BJ153">
+        <v>3.04</v>
+      </c>
+      <c r="BK153">
+        <v>1.56</v>
+      </c>
+      <c r="BL153">
+        <v>2.21</v>
+      </c>
+      <c r="BM153">
+        <v>1.95</v>
+      </c>
+      <c r="BN153">
+        <v>1.76</v>
+      </c>
+      <c r="BO153">
+        <v>2.51</v>
+      </c>
+      <c r="BP153">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7502745</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45669.72916666666</v>
+      </c>
+      <c r="F154">
+        <v>16</v>
+      </c>
+      <c r="G154" t="s">
+        <v>79</v>
+      </c>
+      <c r="H154" t="s">
+        <v>87</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>2</v>
+      </c>
+      <c r="O154" t="s">
+        <v>186</v>
+      </c>
+      <c r="P154" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q154">
+        <v>3.38</v>
+      </c>
+      <c r="R154">
+        <v>2.03</v>
+      </c>
+      <c r="S154">
+        <v>3.18</v>
+      </c>
+      <c r="T154">
+        <v>1.47</v>
+      </c>
+      <c r="U154">
+        <v>2.57</v>
+      </c>
+      <c r="V154">
+        <v>3.1</v>
+      </c>
+      <c r="W154">
+        <v>1.34</v>
+      </c>
+      <c r="X154">
+        <v>7.6</v>
+      </c>
+      <c r="Y154">
+        <v>1.07</v>
+      </c>
+      <c r="Z154">
+        <v>2.55</v>
+      </c>
+      <c r="AA154">
+        <v>3.1</v>
+      </c>
+      <c r="AB154">
+        <v>2.7</v>
+      </c>
+      <c r="AC154">
+        <v>1.05</v>
+      </c>
+      <c r="AD154">
+        <v>6.7</v>
+      </c>
+      <c r="AE154">
+        <v>1.35</v>
+      </c>
+      <c r="AF154">
+        <v>2.75</v>
+      </c>
+      <c r="AG154">
+        <v>2.1</v>
+      </c>
+      <c r="AH154">
+        <v>1.6</v>
+      </c>
+      <c r="AI154">
+        <v>1.85</v>
+      </c>
+      <c r="AJ154">
+        <v>1.85</v>
+      </c>
+      <c r="AK154">
+        <v>1.47</v>
+      </c>
+      <c r="AL154">
+        <v>1.32</v>
+      </c>
+      <c r="AM154">
+        <v>1.44</v>
+      </c>
+      <c r="AN154">
+        <v>1.71</v>
+      </c>
+      <c r="AO154">
+        <v>1.75</v>
+      </c>
+      <c r="AP154">
+        <v>1.63</v>
+      </c>
+      <c r="AQ154">
+        <v>1.67</v>
+      </c>
+      <c r="AR154">
+        <v>1.58</v>
+      </c>
+      <c r="AS154">
+        <v>1.41</v>
+      </c>
+      <c r="AT154">
+        <v>2.99</v>
+      </c>
+      <c r="AU154">
+        <v>8</v>
+      </c>
+      <c r="AV154">
+        <v>4</v>
+      </c>
+      <c r="AW154">
+        <v>3</v>
+      </c>
+      <c r="AX154">
+        <v>6</v>
+      </c>
+      <c r="AY154">
+        <v>11</v>
+      </c>
+      <c r="AZ154">
+        <v>10</v>
+      </c>
+      <c r="BA154">
+        <v>5</v>
+      </c>
+      <c r="BB154">
+        <v>7</v>
+      </c>
+      <c r="BC154">
+        <v>12</v>
+      </c>
+      <c r="BD154">
+        <v>1.79</v>
+      </c>
+      <c r="BE154">
+        <v>7.1</v>
+      </c>
+      <c r="BF154">
+        <v>2.46</v>
+      </c>
+      <c r="BG154">
+        <v>1.14</v>
+      </c>
+      <c r="BH154">
+        <v>4.33</v>
+      </c>
+      <c r="BI154">
+        <v>1.31</v>
+      </c>
+      <c r="BJ154">
+        <v>2.92</v>
+      </c>
+      <c r="BK154">
+        <v>1.57</v>
+      </c>
+      <c r="BL154">
+        <v>2.19</v>
+      </c>
+      <c r="BM154">
+        <v>1.98</v>
+      </c>
+      <c r="BN154">
+        <v>1.74</v>
+      </c>
+      <c r="BO154">
+        <v>2.57</v>
+      </c>
+      <c r="BP154">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
@@ -32249,13 +32249,13 @@
         <v>6</v>
       </c>
       <c r="BA151">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB151">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC151">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD151">
         <v>1.55</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -577,6 +577,21 @@
     <t>['90+6']</t>
   </si>
   <si>
+    <t>['9', '35', '76', '81']</t>
+  </si>
+  <si>
+    <t>['2', '53', '81']</t>
+  </si>
+  <si>
+    <t>['70', '90+6']</t>
+  </si>
+  <si>
+    <t>['20', '65', '78']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -827,6 +842,9 @@
   </si>
   <si>
     <t>['4']</t>
+  </si>
+  <si>
+    <t>['26', '69']</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1444,7 +1462,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1650,7 +1668,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1856,7 +1874,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2268,7 +2286,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2474,7 +2492,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2886,7 +2904,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3298,7 +3316,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3376,10 +3394,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ11">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3710,7 +3728,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3788,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ13">
         <v>1.78</v>
@@ -3916,7 +3934,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4122,7 +4140,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4200,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4328,7 +4346,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4612,10 +4630,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4818,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ18">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4946,7 +4964,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5027,7 +5045,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ19">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5152,7 +5170,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5770,7 +5788,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6057,7 +6075,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ24">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR24">
         <v>1.31</v>
@@ -6182,7 +6200,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6594,7 +6612,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6878,7 +6896,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ28">
         <v>1.11</v>
@@ -7006,7 +7024,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7084,10 +7102,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7212,7 +7230,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7293,7 +7311,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ30">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR30">
         <v>1.33</v>
@@ -7499,7 +7517,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
         <v>1.31</v>
@@ -7624,7 +7642,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7705,7 +7723,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ32">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR32">
         <v>2.27</v>
@@ -7908,7 +7926,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33">
         <v>1.44</v>
@@ -8036,7 +8054,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8114,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ34">
         <v>1.5</v>
@@ -8242,7 +8260,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8448,7 +8466,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8526,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
         <v>0.75</v>
@@ -8860,7 +8878,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9066,7 +9084,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9478,7 +9496,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9684,7 +9702,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9971,7 +9989,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ43">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR43">
         <v>1.55</v>
@@ -10096,7 +10114,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10174,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ44">
         <v>0.63</v>
@@ -10302,7 +10320,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10586,7 +10604,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ46">
         <v>1.25</v>
@@ -10714,7 +10732,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10792,10 +10810,10 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR47">
         <v>1.36</v>
@@ -10920,7 +10938,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11126,7 +11144,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11204,7 +11222,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ49">
         <v>2.38</v>
@@ -11332,7 +11350,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11413,7 +11431,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11538,7 +11556,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11619,7 +11637,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR51">
         <v>1.12</v>
@@ -12028,10 +12046,10 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ53">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR53">
         <v>1.6</v>
@@ -12156,7 +12174,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12568,7 +12586,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12774,7 +12792,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -12855,7 +12873,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR57">
         <v>1.67</v>
@@ -13061,7 +13079,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ58">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR58">
         <v>1.6</v>
@@ -13186,7 +13204,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13676,7 +13694,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ61">
         <v>1.11</v>
@@ -14294,7 +14312,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ64">
         <v>1.56</v>
@@ -14422,7 +14440,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14503,7 +14521,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ65">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -14709,7 +14727,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ66">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR66">
         <v>1.24</v>
@@ -14834,7 +14852,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -14912,7 +14930,7 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ67">
         <v>2.38</v>
@@ -15040,7 +15058,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15327,7 +15345,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ69">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR69">
         <v>1.69</v>
@@ -15530,7 +15548,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ70">
         <v>0.88</v>
@@ -16070,7 +16088,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16151,7 +16169,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR73">
         <v>1.18</v>
@@ -16276,7 +16294,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16482,7 +16500,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16560,7 +16578,7 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ75">
         <v>1.33</v>
@@ -16688,7 +16706,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -16766,7 +16784,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ76">
         <v>1.67</v>
@@ -17100,7 +17118,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17387,7 +17405,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR79">
         <v>1.3</v>
@@ -17512,7 +17530,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17796,7 +17814,7 @@
         <v>1.25</v>
       </c>
       <c r="AP81">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ81">
         <v>0.88</v>
@@ -18002,7 +18020,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ82">
         <v>1.11</v>
@@ -18130,7 +18148,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18414,7 +18432,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>1.25</v>
@@ -18748,7 +18766,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19035,7 +19053,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ87">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR87">
         <v>1.38</v>
@@ -19160,7 +19178,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19241,7 +19259,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR88">
         <v>1.05</v>
@@ -19572,7 +19590,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19778,7 +19796,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -19859,7 +19877,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ91">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR91">
         <v>1.19</v>
@@ -19984,7 +20002,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20190,7 +20208,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20271,7 +20289,7 @@
         <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -20396,7 +20414,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20474,7 +20492,7 @@
         <v>2.2</v>
       </c>
       <c r="AP94">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ94">
         <v>1.67</v>
@@ -20602,7 +20620,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20683,7 +20701,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ95">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR95">
         <v>1.56</v>
@@ -21014,7 +21032,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21092,7 +21110,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ97">
         <v>1.33</v>
@@ -21220,7 +21238,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21426,7 +21444,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21504,7 +21522,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ99">
         <v>1.5</v>
@@ -21710,7 +21728,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ100">
         <v>1.44</v>
@@ -22125,7 +22143,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ102">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22250,7 +22268,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22331,7 +22349,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ103">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR103">
         <v>1.71</v>
@@ -22662,7 +22680,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22740,7 +22758,7 @@
         <v>1.67</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ105">
         <v>1.56</v>
@@ -22868,7 +22886,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -22946,7 +22964,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ106">
         <v>1.11</v>
@@ -23074,7 +23092,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23280,7 +23298,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23486,7 +23504,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23976,7 +23994,7 @@
         <v>2.6</v>
       </c>
       <c r="AP111">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ111">
         <v>2.38</v>
@@ -24185,7 +24203,7 @@
         <v>2</v>
       </c>
       <c r="AQ112">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR112">
         <v>1.41</v>
@@ -24310,7 +24328,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24388,7 +24406,7 @@
         <v>1.17</v>
       </c>
       <c r="AP113">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ113">
         <v>1.78</v>
@@ -24516,7 +24534,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24597,7 +24615,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR114">
         <v>1.37</v>
@@ -24928,7 +24946,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25134,7 +25152,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25340,7 +25358,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25418,10 +25436,10 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ118">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -26036,7 +26054,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ121">
         <v>1.56</v>
@@ -26164,7 +26182,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26245,7 +26263,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ122">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR122">
         <v>1.24</v>
@@ -26576,7 +26594,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26988,7 +27006,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27069,7 +27087,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ126">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27400,7 +27418,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27812,7 +27830,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -27893,7 +27911,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ130">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28096,10 +28114,10 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ131">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28224,7 +28242,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28302,7 +28320,7 @@
         <v>1.86</v>
       </c>
       <c r="AP132">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ132">
         <v>1.67</v>
@@ -28430,7 +28448,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28636,7 +28654,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29126,10 +29144,10 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ136">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR136">
         <v>1.47</v>
@@ -29254,7 +29272,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29666,7 +29684,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -29950,7 +29968,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ140">
         <v>1.33</v>
@@ -30078,7 +30096,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30156,7 +30174,7 @@
         <v>2.29</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ141">
         <v>2.38</v>
@@ -30362,10 +30380,10 @@
         <v>0.71</v>
       </c>
       <c r="AP142">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ142">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR142">
         <v>1.66</v>
@@ -30490,7 +30508,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30696,7 +30714,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30777,7 +30795,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ144">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR144">
         <v>1.17</v>
@@ -31108,7 +31126,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31314,7 +31332,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31395,7 +31413,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ147">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR147">
         <v>1.68</v>
@@ -31520,7 +31538,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31598,10 +31616,10 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ148">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR148">
         <v>1.62</v>
@@ -32138,7 +32156,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32344,7 +32362,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32425,7 +32443,7 @@
         <v>2</v>
       </c>
       <c r="AQ152">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR152">
         <v>1.34</v>
@@ -32550,7 +32568,7 @@
         <v>140</v>
       </c>
       <c r="P153" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q153">
         <v>2.96</v>
@@ -32756,7 +32774,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -32834,7 +32852,7 @@
         <v>1.75</v>
       </c>
       <c r="AP154">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ154">
         <v>1.67</v>
@@ -32913,6 +32931,1036 @@
       </c>
       <c r="BP154">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7502758</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45674.625</v>
+      </c>
+      <c r="F155">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>86</v>
+      </c>
+      <c r="H155" t="s">
+        <v>72</v>
+      </c>
+      <c r="I155">
+        <v>2</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+      <c r="L155">
+        <v>4</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>4</v>
+      </c>
+      <c r="O155" t="s">
+        <v>187</v>
+      </c>
+      <c r="P155" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q155">
+        <v>2.7</v>
+      </c>
+      <c r="R155">
+        <v>2.05</v>
+      </c>
+      <c r="S155">
+        <v>3.8</v>
+      </c>
+      <c r="T155">
+        <v>1.42</v>
+      </c>
+      <c r="U155">
+        <v>2.65</v>
+      </c>
+      <c r="V155">
+        <v>2.95</v>
+      </c>
+      <c r="W155">
+        <v>1.35</v>
+      </c>
+      <c r="X155">
+        <v>7.75</v>
+      </c>
+      <c r="Y155">
+        <v>1.07</v>
+      </c>
+      <c r="Z155">
+        <v>2.13</v>
+      </c>
+      <c r="AA155">
+        <v>3.35</v>
+      </c>
+      <c r="AB155">
+        <v>3.55</v>
+      </c>
+      <c r="AC155">
+        <v>1.06</v>
+      </c>
+      <c r="AD155">
+        <v>8</v>
+      </c>
+      <c r="AE155">
+        <v>1.35</v>
+      </c>
+      <c r="AF155">
+        <v>3</v>
+      </c>
+      <c r="AG155">
+        <v>2</v>
+      </c>
+      <c r="AH155">
+        <v>1.73</v>
+      </c>
+      <c r="AI155">
+        <v>1.83</v>
+      </c>
+      <c r="AJ155">
+        <v>1.85</v>
+      </c>
+      <c r="AK155">
+        <v>1.3</v>
+      </c>
+      <c r="AL155">
+        <v>1.3</v>
+      </c>
+      <c r="AM155">
+        <v>1.7</v>
+      </c>
+      <c r="AN155">
+        <v>2.11</v>
+      </c>
+      <c r="AO155">
+        <v>0.63</v>
+      </c>
+      <c r="AP155">
+        <v>2.2</v>
+      </c>
+      <c r="AQ155">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR155">
+        <v>1.55</v>
+      </c>
+      <c r="AS155">
+        <v>1.34</v>
+      </c>
+      <c r="AT155">
+        <v>2.89</v>
+      </c>
+      <c r="AU155">
+        <v>5</v>
+      </c>
+      <c r="AV155">
+        <v>3</v>
+      </c>
+      <c r="AW155">
+        <v>8</v>
+      </c>
+      <c r="AX155">
+        <v>2</v>
+      </c>
+      <c r="AY155">
+        <v>13</v>
+      </c>
+      <c r="AZ155">
+        <v>5</v>
+      </c>
+      <c r="BA155">
+        <v>5</v>
+      </c>
+      <c r="BB155">
+        <v>3</v>
+      </c>
+      <c r="BC155">
+        <v>8</v>
+      </c>
+      <c r="BD155">
+        <v>1.82</v>
+      </c>
+      <c r="BE155">
+        <v>8</v>
+      </c>
+      <c r="BF155">
+        <v>2.33</v>
+      </c>
+      <c r="BG155">
+        <v>1.25</v>
+      </c>
+      <c r="BH155">
+        <v>3.75</v>
+      </c>
+      <c r="BI155">
+        <v>1.45</v>
+      </c>
+      <c r="BJ155">
+        <v>2.63</v>
+      </c>
+      <c r="BK155">
+        <v>1.74</v>
+      </c>
+      <c r="BL155">
+        <v>2.02</v>
+      </c>
+      <c r="BM155">
+        <v>2.19</v>
+      </c>
+      <c r="BN155">
+        <v>1.63</v>
+      </c>
+      <c r="BO155">
+        <v>2.82</v>
+      </c>
+      <c r="BP155">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7502762</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45674.71875</v>
+      </c>
+      <c r="F156">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>85</v>
+      </c>
+      <c r="H156" t="s">
+        <v>73</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>3</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>3</v>
+      </c>
+      <c r="O156" t="s">
+        <v>188</v>
+      </c>
+      <c r="P156" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q156">
+        <v>2.87</v>
+      </c>
+      <c r="R156">
+        <v>1.98</v>
+      </c>
+      <c r="S156">
+        <v>3.75</v>
+      </c>
+      <c r="T156">
+        <v>1.47</v>
+      </c>
+      <c r="U156">
+        <v>2.45</v>
+      </c>
+      <c r="V156">
+        <v>3.2</v>
+      </c>
+      <c r="W156">
+        <v>1.31</v>
+      </c>
+      <c r="X156">
+        <v>8.75</v>
+      </c>
+      <c r="Y156">
+        <v>1.06</v>
+      </c>
+      <c r="Z156">
+        <v>2.24</v>
+      </c>
+      <c r="AA156">
+        <v>3.2</v>
+      </c>
+      <c r="AB156">
+        <v>3.45</v>
+      </c>
+      <c r="AC156">
+        <v>1.08</v>
+      </c>
+      <c r="AD156">
+        <v>7</v>
+      </c>
+      <c r="AE156">
+        <v>1.42</v>
+      </c>
+      <c r="AF156">
+        <v>2.75</v>
+      </c>
+      <c r="AG156">
+        <v>2.25</v>
+      </c>
+      <c r="AH156">
+        <v>1.62</v>
+      </c>
+      <c r="AI156">
+        <v>1.95</v>
+      </c>
+      <c r="AJ156">
+        <v>1.75</v>
+      </c>
+      <c r="AK156">
+        <v>1.33</v>
+      </c>
+      <c r="AL156">
+        <v>1.33</v>
+      </c>
+      <c r="AM156">
+        <v>1.61</v>
+      </c>
+      <c r="AN156">
+        <v>1.5</v>
+      </c>
+      <c r="AO156">
+        <v>1.33</v>
+      </c>
+      <c r="AP156">
+        <v>1.67</v>
+      </c>
+      <c r="AQ156">
+        <v>1.2</v>
+      </c>
+      <c r="AR156">
+        <v>1.49</v>
+      </c>
+      <c r="AS156">
+        <v>1.31</v>
+      </c>
+      <c r="AT156">
+        <v>2.8</v>
+      </c>
+      <c r="AU156">
+        <v>6</v>
+      </c>
+      <c r="AV156">
+        <v>4</v>
+      </c>
+      <c r="AW156">
+        <v>8</v>
+      </c>
+      <c r="AX156">
+        <v>4</v>
+      </c>
+      <c r="AY156">
+        <v>14</v>
+      </c>
+      <c r="AZ156">
+        <v>8</v>
+      </c>
+      <c r="BA156">
+        <v>7</v>
+      </c>
+      <c r="BB156">
+        <v>7</v>
+      </c>
+      <c r="BC156">
+        <v>14</v>
+      </c>
+      <c r="BD156">
+        <v>1.64</v>
+      </c>
+      <c r="BE156">
+        <v>8.5</v>
+      </c>
+      <c r="BF156">
+        <v>2.66</v>
+      </c>
+      <c r="BG156">
+        <v>1.15</v>
+      </c>
+      <c r="BH156">
+        <v>4.95</v>
+      </c>
+      <c r="BI156">
+        <v>1.29</v>
+      </c>
+      <c r="BJ156">
+        <v>3.38</v>
+      </c>
+      <c r="BK156">
+        <v>1.51</v>
+      </c>
+      <c r="BL156">
+        <v>2.46</v>
+      </c>
+      <c r="BM156">
+        <v>1.82</v>
+      </c>
+      <c r="BN156">
+        <v>1.93</v>
+      </c>
+      <c r="BO156">
+        <v>2.27</v>
+      </c>
+      <c r="BP156">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7502760</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45675.33333333334</v>
+      </c>
+      <c r="F157">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>79</v>
+      </c>
+      <c r="H157" t="s">
+        <v>76</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>2</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>2</v>
+      </c>
+      <c r="O157" t="s">
+        <v>189</v>
+      </c>
+      <c r="P157" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q157">
+        <v>2.51</v>
+      </c>
+      <c r="R157">
+        <v>2.16</v>
+      </c>
+      <c r="S157">
+        <v>4.1</v>
+      </c>
+      <c r="T157">
+        <v>1.39</v>
+      </c>
+      <c r="U157">
+        <v>2.86</v>
+      </c>
+      <c r="V157">
+        <v>2.7</v>
+      </c>
+      <c r="W157">
+        <v>1.43</v>
+      </c>
+      <c r="X157">
+        <v>6.4</v>
+      </c>
+      <c r="Y157">
+        <v>1.1</v>
+      </c>
+      <c r="Z157">
+        <v>1.96</v>
+      </c>
+      <c r="AA157">
+        <v>3.16</v>
+      </c>
+      <c r="AB157">
+        <v>3.4</v>
+      </c>
+      <c r="AC157">
+        <v>1.02</v>
+      </c>
+      <c r="AD157">
+        <v>7.8</v>
+      </c>
+      <c r="AE157">
+        <v>1.26</v>
+      </c>
+      <c r="AF157">
+        <v>3.22</v>
+      </c>
+      <c r="AG157">
+        <v>1.96</v>
+      </c>
+      <c r="AH157">
+        <v>1.9</v>
+      </c>
+      <c r="AI157">
+        <v>1.73</v>
+      </c>
+      <c r="AJ157">
+        <v>1.99</v>
+      </c>
+      <c r="AK157">
+        <v>1.28</v>
+      </c>
+      <c r="AL157">
+        <v>1.28</v>
+      </c>
+      <c r="AM157">
+        <v>1.77</v>
+      </c>
+      <c r="AN157">
+        <v>1.63</v>
+      </c>
+      <c r="AO157">
+        <v>0.33</v>
+      </c>
+      <c r="AP157">
+        <v>1.78</v>
+      </c>
+      <c r="AQ157">
+        <v>0.3</v>
+      </c>
+      <c r="AR157">
+        <v>1.59</v>
+      </c>
+      <c r="AS157">
+        <v>1.5</v>
+      </c>
+      <c r="AT157">
+        <v>3.09</v>
+      </c>
+      <c r="AU157">
+        <v>10</v>
+      </c>
+      <c r="AV157">
+        <v>10</v>
+      </c>
+      <c r="AW157">
+        <v>4</v>
+      </c>
+      <c r="AX157">
+        <v>4</v>
+      </c>
+      <c r="AY157">
+        <v>14</v>
+      </c>
+      <c r="AZ157">
+        <v>14</v>
+      </c>
+      <c r="BA157">
+        <v>-1</v>
+      </c>
+      <c r="BB157">
+        <v>-1</v>
+      </c>
+      <c r="BC157">
+        <v>-1</v>
+      </c>
+      <c r="BD157">
+        <v>1.82</v>
+      </c>
+      <c r="BE157">
+        <v>8</v>
+      </c>
+      <c r="BF157">
+        <v>2.33</v>
+      </c>
+      <c r="BG157">
+        <v>1.23</v>
+      </c>
+      <c r="BH157">
+        <v>3.92</v>
+      </c>
+      <c r="BI157">
+        <v>1.42</v>
+      </c>
+      <c r="BJ157">
+        <v>2.73</v>
+      </c>
+      <c r="BK157">
+        <v>1.69</v>
+      </c>
+      <c r="BL157">
+        <v>2.09</v>
+      </c>
+      <c r="BM157">
+        <v>2.11</v>
+      </c>
+      <c r="BN157">
+        <v>1.68</v>
+      </c>
+      <c r="BO157">
+        <v>2.72</v>
+      </c>
+      <c r="BP157">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7502763</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45675.45833333334</v>
+      </c>
+      <c r="F158">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>81</v>
+      </c>
+      <c r="H158" t="s">
+        <v>78</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>2</v>
+      </c>
+      <c r="L158">
+        <v>3</v>
+      </c>
+      <c r="M158">
+        <v>2</v>
+      </c>
+      <c r="N158">
+        <v>5</v>
+      </c>
+      <c r="O158" t="s">
+        <v>190</v>
+      </c>
+      <c r="P158" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q158">
+        <v>3.5</v>
+      </c>
+      <c r="R158">
+        <v>2.05</v>
+      </c>
+      <c r="S158">
+        <v>3</v>
+      </c>
+      <c r="T158">
+        <v>1.44</v>
+      </c>
+      <c r="U158">
+        <v>2.6</v>
+      </c>
+      <c r="V158">
+        <v>2.95</v>
+      </c>
+      <c r="W158">
+        <v>1.35</v>
+      </c>
+      <c r="X158">
+        <v>7.4</v>
+      </c>
+      <c r="Y158">
+        <v>1.06</v>
+      </c>
+      <c r="Z158">
+        <v>2.8</v>
+      </c>
+      <c r="AA158">
+        <v>3.08</v>
+      </c>
+      <c r="AB158">
+        <v>2.27</v>
+      </c>
+      <c r="AC158">
+        <v>1.03</v>
+      </c>
+      <c r="AD158">
+        <v>7.2</v>
+      </c>
+      <c r="AE158">
+        <v>1.33</v>
+      </c>
+      <c r="AF158">
+        <v>3.2</v>
+      </c>
+      <c r="AG158">
+        <v>2.08</v>
+      </c>
+      <c r="AH158">
+        <v>1.78</v>
+      </c>
+      <c r="AI158">
+        <v>1.75</v>
+      </c>
+      <c r="AJ158">
+        <v>2</v>
+      </c>
+      <c r="AK158">
+        <v>1.57</v>
+      </c>
+      <c r="AL158">
+        <v>1.28</v>
+      </c>
+      <c r="AM158">
+        <v>1.38</v>
+      </c>
+      <c r="AN158">
+        <v>1</v>
+      </c>
+      <c r="AO158">
+        <v>1.5</v>
+      </c>
+      <c r="AP158">
+        <v>1.22</v>
+      </c>
+      <c r="AQ158">
+        <v>1.33</v>
+      </c>
+      <c r="AR158">
+        <v>1.37</v>
+      </c>
+      <c r="AS158">
+        <v>1.46</v>
+      </c>
+      <c r="AT158">
+        <v>2.83</v>
+      </c>
+      <c r="AU158">
+        <v>6</v>
+      </c>
+      <c r="AV158">
+        <v>6</v>
+      </c>
+      <c r="AW158">
+        <v>2</v>
+      </c>
+      <c r="AX158">
+        <v>11</v>
+      </c>
+      <c r="AY158">
+        <v>8</v>
+      </c>
+      <c r="AZ158">
+        <v>17</v>
+      </c>
+      <c r="BA158">
+        <v>4</v>
+      </c>
+      <c r="BB158">
+        <v>5</v>
+      </c>
+      <c r="BC158">
+        <v>9</v>
+      </c>
+      <c r="BD158">
+        <v>2.9</v>
+      </c>
+      <c r="BE158">
+        <v>9</v>
+      </c>
+      <c r="BF158">
+        <v>1.55</v>
+      </c>
+      <c r="BG158">
+        <v>1.17</v>
+      </c>
+      <c r="BH158">
+        <v>4.7</v>
+      </c>
+      <c r="BI158">
+        <v>1.31</v>
+      </c>
+      <c r="BJ158">
+        <v>3.25</v>
+      </c>
+      <c r="BK158">
+        <v>1.54</v>
+      </c>
+      <c r="BL158">
+        <v>2.38</v>
+      </c>
+      <c r="BM158">
+        <v>1.87</v>
+      </c>
+      <c r="BN158">
+        <v>1.87</v>
+      </c>
+      <c r="BO158">
+        <v>2.35</v>
+      </c>
+      <c r="BP158">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7502757</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45675.52083333334</v>
+      </c>
+      <c r="F159">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>83</v>
+      </c>
+      <c r="H159" t="s">
+        <v>75</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>2</v>
+      </c>
+      <c r="L159">
+        <v>1</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>2</v>
+      </c>
+      <c r="O159" t="s">
+        <v>191</v>
+      </c>
+      <c r="P159" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q159">
+        <v>3.12</v>
+      </c>
+      <c r="R159">
+        <v>1.97</v>
+      </c>
+      <c r="S159">
+        <v>3.6</v>
+      </c>
+      <c r="T159">
+        <v>1.49</v>
+      </c>
+      <c r="U159">
+        <v>2.51</v>
+      </c>
+      <c r="V159">
+        <v>3.34</v>
+      </c>
+      <c r="W159">
+        <v>1.3</v>
+      </c>
+      <c r="X159">
+        <v>9</v>
+      </c>
+      <c r="Y159">
+        <v>1.04</v>
+      </c>
+      <c r="Z159">
+        <v>2.55</v>
+      </c>
+      <c r="AA159">
+        <v>2.9</v>
+      </c>
+      <c r="AB159">
+        <v>2.85</v>
+      </c>
+      <c r="AC159">
+        <v>1.04</v>
+      </c>
+      <c r="AD159">
+        <v>6.95</v>
+      </c>
+      <c r="AE159">
+        <v>1.38</v>
+      </c>
+      <c r="AF159">
+        <v>2.63</v>
+      </c>
+      <c r="AG159">
+        <v>2.25</v>
+      </c>
+      <c r="AH159">
+        <v>1.57</v>
+      </c>
+      <c r="AI159">
+        <v>1.94</v>
+      </c>
+      <c r="AJ159">
+        <v>1.77</v>
+      </c>
+      <c r="AK159">
+        <v>1.4</v>
+      </c>
+      <c r="AL159">
+        <v>1.33</v>
+      </c>
+      <c r="AM159">
+        <v>1.5</v>
+      </c>
+      <c r="AN159">
+        <v>1.78</v>
+      </c>
+      <c r="AO159">
+        <v>1.38</v>
+      </c>
+      <c r="AP159">
+        <v>1.7</v>
+      </c>
+      <c r="AQ159">
+        <v>1.33</v>
+      </c>
+      <c r="AR159">
+        <v>1.72</v>
+      </c>
+      <c r="AS159">
+        <v>1.35</v>
+      </c>
+      <c r="AT159">
+        <v>3.07</v>
+      </c>
+      <c r="AU159">
+        <v>7</v>
+      </c>
+      <c r="AV159">
+        <v>8</v>
+      </c>
+      <c r="AW159">
+        <v>9</v>
+      </c>
+      <c r="AX159">
+        <v>5</v>
+      </c>
+      <c r="AY159">
+        <v>16</v>
+      </c>
+      <c r="AZ159">
+        <v>13</v>
+      </c>
+      <c r="BA159">
+        <v>-1</v>
+      </c>
+      <c r="BB159">
+        <v>-1</v>
+      </c>
+      <c r="BC159">
+        <v>-1</v>
+      </c>
+      <c r="BD159">
+        <v>2.2</v>
+      </c>
+      <c r="BE159">
+        <v>8</v>
+      </c>
+      <c r="BF159">
+        <v>1.83</v>
+      </c>
+      <c r="BG159">
+        <v>1.22</v>
+      </c>
+      <c r="BH159">
+        <v>4</v>
+      </c>
+      <c r="BI159">
+        <v>1.41</v>
+      </c>
+      <c r="BJ159">
+        <v>2.77</v>
+      </c>
+      <c r="BK159">
+        <v>1.68</v>
+      </c>
+      <c r="BL159">
+        <v>2.11</v>
+      </c>
+      <c r="BM159">
+        <v>2.09</v>
+      </c>
+      <c r="BN159">
+        <v>1.69</v>
+      </c>
+      <c r="BO159">
+        <v>2.68</v>
+      </c>
+      <c r="BP159">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="280">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,12 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['45', '83']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -845,6 +851,9 @@
   </si>
   <si>
     <t>['26', '69']</t>
+  </si>
+  <si>
+    <t>['90']</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1462,7 +1471,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1668,7 +1677,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1874,7 +1883,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2286,7 +2295,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2492,7 +2501,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2904,7 +2913,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3316,7 +3325,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3603,7 +3612,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ12">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3728,7 +3737,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3809,7 +3818,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ13">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3934,7 +3943,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4012,10 +4021,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4140,7 +4149,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4346,7 +4355,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4424,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ16">
         <v>2.38</v>
@@ -4964,7 +4973,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5042,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>0.3</v>
@@ -5170,7 +5179,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5788,7 +5797,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6200,7 +6209,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6612,7 +6621,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7024,7 +7033,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7230,7 +7239,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7514,7 +7523,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>1.33</v>
@@ -7642,7 +7651,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7720,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ32">
         <v>1.33</v>
@@ -7929,7 +7938,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ33">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR33">
         <v>1.04</v>
@@ -8054,7 +8063,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8260,7 +8269,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8338,7 +8347,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ35">
         <v>2.38</v>
@@ -8466,7 +8475,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8547,7 +8556,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ36">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR36">
         <v>0.91</v>
@@ -8753,7 +8762,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR37">
         <v>0.82</v>
@@ -8878,7 +8887,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9084,7 +9093,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9371,7 +9380,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ40">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9496,7 +9505,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9702,7 +9711,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10114,7 +10123,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10320,7 +10329,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10732,7 +10741,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10938,7 +10947,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11016,7 +11025,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ48">
         <v>1.5</v>
@@ -11144,7 +11153,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11350,7 +11359,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11428,7 +11437,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>1.2</v>
@@ -11556,7 +11565,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12174,7 +12183,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12255,7 +12264,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR54">
         <v>1.11</v>
@@ -12458,10 +12467,10 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ55">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12586,7 +12595,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12792,7 +12801,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13204,7 +13213,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13903,7 +13912,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ62">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR62">
         <v>1.41</v>
@@ -14440,7 +14449,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14724,7 +14733,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>0.5600000000000001</v>
@@ -14852,7 +14861,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15058,7 +15067,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15139,7 +15148,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15342,7 +15351,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ69">
         <v>1.33</v>
@@ -15757,7 +15766,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ71">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR71">
         <v>0.8</v>
@@ -15960,7 +15969,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ72">
         <v>1.11</v>
@@ -16088,7 +16097,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16294,7 +16303,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16500,7 +16509,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16706,7 +16715,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17118,7 +17127,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17199,7 +17208,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ78">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17530,7 +17539,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17611,7 +17620,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR80">
         <v>1.09</v>
@@ -18148,7 +18157,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18766,7 +18775,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -18847,7 +18856,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ86">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19178,7 +19187,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19462,7 +19471,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
         <v>0.63</v>
@@ -19590,7 +19599,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19668,7 +19677,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ90">
         <v>1.56</v>
@@ -19796,7 +19805,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20002,7 +20011,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20208,7 +20217,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20414,7 +20423,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20620,7 +20629,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20698,7 +20707,7 @@
         <v>0.4</v>
       </c>
       <c r="AP95">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ95">
         <v>0.3</v>
@@ -20907,7 +20916,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR96">
         <v>1.37</v>
@@ -21032,7 +21041,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21238,7 +21247,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21319,7 +21328,7 @@
         <v>2</v>
       </c>
       <c r="AQ98">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21444,7 +21453,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21731,7 +21740,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ100">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -21934,7 +21943,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ101">
         <v>0.63</v>
@@ -22268,7 +22277,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22680,7 +22689,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22886,7 +22895,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23092,7 +23101,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23173,7 +23182,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ107">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23298,7 +23307,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23376,7 +23385,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ108">
         <v>1.25</v>
@@ -23504,7 +23513,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24328,7 +24337,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24409,7 +24418,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ113">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24534,7 +24543,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24818,7 +24827,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -24946,7 +24955,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25152,7 +25161,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25233,7 +25242,7 @@
         <v>1</v>
       </c>
       <c r="AQ117">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.26</v>
@@ -25358,7 +25367,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25642,7 +25651,7 @@
         <v>2</v>
       </c>
       <c r="AP119">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ119">
         <v>1.67</v>
@@ -26182,7 +26191,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26594,7 +26603,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26878,7 +26887,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>1.33</v>
@@ -27006,7 +27015,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27418,7 +27427,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27705,7 +27714,7 @@
         <v>2</v>
       </c>
       <c r="AQ129">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -27830,7 +27839,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -27908,7 +27917,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ130">
         <v>0.3</v>
@@ -28242,7 +28251,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28448,7 +28457,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28526,7 +28535,7 @@
         <v>1.29</v>
       </c>
       <c r="AP133">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ133">
         <v>1.33</v>
@@ -28654,7 +28663,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28735,7 +28744,7 @@
         <v>0.44</v>
       </c>
       <c r="AQ134">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR134">
         <v>1.14</v>
@@ -29272,7 +29281,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29684,7 +29693,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30096,7 +30105,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30508,7 +30517,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30586,10 +30595,10 @@
         <v>1.63</v>
       </c>
       <c r="AP143">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30714,7 +30723,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31001,7 +31010,7 @@
         <v>2</v>
       </c>
       <c r="AQ145">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR145">
         <v>1.33</v>
@@ -31126,7 +31135,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31204,10 +31213,10 @@
         <v>1.63</v>
       </c>
       <c r="AP146">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ146">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR146">
         <v>1.64</v>
@@ -31332,7 +31341,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31410,7 +31419,7 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ147">
         <v>1.2</v>
@@ -31538,7 +31547,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32156,7 +32165,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32362,7 +32371,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32568,7 +32577,7 @@
         <v>140</v>
       </c>
       <c r="P153" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q153">
         <v>2.96</v>
@@ -32774,7 +32783,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33503,13 +33512,13 @@
         <v>14</v>
       </c>
       <c r="BA157">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB157">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BC157">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BD157">
         <v>1.82</v>
@@ -33598,7 +33607,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33915,13 +33924,13 @@
         <v>13</v>
       </c>
       <c r="BA159">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB159">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC159">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD159">
         <v>2.2</v>
@@ -33961,6 +33970,624 @@
       </c>
       <c r="BP159">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7502761</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45676.33333333334</v>
+      </c>
+      <c r="F160">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>84</v>
+      </c>
+      <c r="H160" t="s">
+        <v>77</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
+        <v>192</v>
+      </c>
+      <c r="P160" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q160">
+        <v>2.75</v>
+      </c>
+      <c r="R160">
+        <v>1.97</v>
+      </c>
+      <c r="S160">
+        <v>4.3</v>
+      </c>
+      <c r="T160">
+        <v>1.49</v>
+      </c>
+      <c r="U160">
+        <v>2.51</v>
+      </c>
+      <c r="V160">
+        <v>3.34</v>
+      </c>
+      <c r="W160">
+        <v>1.3</v>
+      </c>
+      <c r="X160">
+        <v>9.4</v>
+      </c>
+      <c r="Y160">
+        <v>1.04</v>
+      </c>
+      <c r="Z160">
+        <v>2</v>
+      </c>
+      <c r="AA160">
+        <v>3.2</v>
+      </c>
+      <c r="AB160">
+        <v>3.67</v>
+      </c>
+      <c r="AC160">
+        <v>1.03</v>
+      </c>
+      <c r="AD160">
+        <v>7.3</v>
+      </c>
+      <c r="AE160">
+        <v>1.38</v>
+      </c>
+      <c r="AF160">
+        <v>2.63</v>
+      </c>
+      <c r="AG160">
+        <v>2.16</v>
+      </c>
+      <c r="AH160">
+        <v>1.62</v>
+      </c>
+      <c r="AI160">
+        <v>1.99</v>
+      </c>
+      <c r="AJ160">
+        <v>1.73</v>
+      </c>
+      <c r="AK160">
+        <v>1.28</v>
+      </c>
+      <c r="AL160">
+        <v>1.32</v>
+      </c>
+      <c r="AM160">
+        <v>1.7</v>
+      </c>
+      <c r="AN160">
+        <v>1.38</v>
+      </c>
+      <c r="AO160">
+        <v>1.78</v>
+      </c>
+      <c r="AP160">
+        <v>1.56</v>
+      </c>
+      <c r="AQ160">
+        <v>1.6</v>
+      </c>
+      <c r="AR160">
+        <v>1.7</v>
+      </c>
+      <c r="AS160">
+        <v>1.47</v>
+      </c>
+      <c r="AT160">
+        <v>3.17</v>
+      </c>
+      <c r="AU160">
+        <v>5</v>
+      </c>
+      <c r="AV160">
+        <v>2</v>
+      </c>
+      <c r="AW160">
+        <v>6</v>
+      </c>
+      <c r="AX160">
+        <v>2</v>
+      </c>
+      <c r="AY160">
+        <v>11</v>
+      </c>
+      <c r="AZ160">
+        <v>4</v>
+      </c>
+      <c r="BA160">
+        <v>6</v>
+      </c>
+      <c r="BB160">
+        <v>6</v>
+      </c>
+      <c r="BC160">
+        <v>12</v>
+      </c>
+      <c r="BD160">
+        <v>1.64</v>
+      </c>
+      <c r="BE160">
+        <v>8.5</v>
+      </c>
+      <c r="BF160">
+        <v>2.76</v>
+      </c>
+      <c r="BG160">
+        <v>1.14</v>
+      </c>
+      <c r="BH160">
+        <v>4.4</v>
+      </c>
+      <c r="BI160">
+        <v>1.3</v>
+      </c>
+      <c r="BJ160">
+        <v>2.97</v>
+      </c>
+      <c r="BK160">
+        <v>1.56</v>
+      </c>
+      <c r="BL160">
+        <v>2.21</v>
+      </c>
+      <c r="BM160">
+        <v>2</v>
+      </c>
+      <c r="BN160">
+        <v>1.8</v>
+      </c>
+      <c r="BO160">
+        <v>2.51</v>
+      </c>
+      <c r="BP160">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7502764</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F161">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>82</v>
+      </c>
+      <c r="H161" t="s">
+        <v>71</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="L161">
+        <v>2</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>3</v>
+      </c>
+      <c r="O161" t="s">
+        <v>193</v>
+      </c>
+      <c r="P161" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q161">
+        <v>3</v>
+      </c>
+      <c r="R161">
+        <v>1.98</v>
+      </c>
+      <c r="S161">
+        <v>3.75</v>
+      </c>
+      <c r="T161">
+        <v>1.49</v>
+      </c>
+      <c r="U161">
+        <v>2.51</v>
+      </c>
+      <c r="V161">
+        <v>3.28</v>
+      </c>
+      <c r="W161">
+        <v>1.31</v>
+      </c>
+      <c r="X161">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y161">
+        <v>1.05</v>
+      </c>
+      <c r="Z161">
+        <v>2.35</v>
+      </c>
+      <c r="AA161">
+        <v>3.25</v>
+      </c>
+      <c r="AB161">
+        <v>2.84</v>
+      </c>
+      <c r="AC161">
+        <v>1.04</v>
+      </c>
+      <c r="AD161">
+        <v>7.1</v>
+      </c>
+      <c r="AE161">
+        <v>1.38</v>
+      </c>
+      <c r="AF161">
+        <v>2.63</v>
+      </c>
+      <c r="AG161">
+        <v>2.07</v>
+      </c>
+      <c r="AH161">
+        <v>1.67</v>
+      </c>
+      <c r="AI161">
+        <v>1.93</v>
+      </c>
+      <c r="AJ161">
+        <v>1.78</v>
+      </c>
+      <c r="AK161">
+        <v>1.36</v>
+      </c>
+      <c r="AL161">
+        <v>1.33</v>
+      </c>
+      <c r="AM161">
+        <v>1.55</v>
+      </c>
+      <c r="AN161">
+        <v>0.89</v>
+      </c>
+      <c r="AO161">
+        <v>0.75</v>
+      </c>
+      <c r="AP161">
+        <v>1.1</v>
+      </c>
+      <c r="AQ161">
+        <v>0.67</v>
+      </c>
+      <c r="AR161">
+        <v>1.7</v>
+      </c>
+      <c r="AS161">
+        <v>1.13</v>
+      </c>
+      <c r="AT161">
+        <v>2.83</v>
+      </c>
+      <c r="AU161">
+        <v>7</v>
+      </c>
+      <c r="AV161">
+        <v>7</v>
+      </c>
+      <c r="AW161">
+        <v>9</v>
+      </c>
+      <c r="AX161">
+        <v>9</v>
+      </c>
+      <c r="AY161">
+        <v>16</v>
+      </c>
+      <c r="AZ161">
+        <v>16</v>
+      </c>
+      <c r="BA161">
+        <v>-1</v>
+      </c>
+      <c r="BB161">
+        <v>-1</v>
+      </c>
+      <c r="BC161">
+        <v>-1</v>
+      </c>
+      <c r="BD161">
+        <v>1.75</v>
+      </c>
+      <c r="BE161">
+        <v>8.5</v>
+      </c>
+      <c r="BF161">
+        <v>2.43</v>
+      </c>
+      <c r="BG161">
+        <v>1.15</v>
+      </c>
+      <c r="BH161">
+        <v>4.25</v>
+      </c>
+      <c r="BI161">
+        <v>1.31</v>
+      </c>
+      <c r="BJ161">
+        <v>2.92</v>
+      </c>
+      <c r="BK161">
+        <v>1.58</v>
+      </c>
+      <c r="BL161">
+        <v>2.17</v>
+      </c>
+      <c r="BM161">
+        <v>1.99</v>
+      </c>
+      <c r="BN161">
+        <v>1.73</v>
+      </c>
+      <c r="BO161">
+        <v>2.57</v>
+      </c>
+      <c r="BP161">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7502765</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45676.52083333334</v>
+      </c>
+      <c r="F162">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>87</v>
+      </c>
+      <c r="H162" t="s">
+        <v>70</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162" t="s">
+        <v>89</v>
+      </c>
+      <c r="P162" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q162">
+        <v>2.79</v>
+      </c>
+      <c r="R162">
+        <v>2.06</v>
+      </c>
+      <c r="S162">
+        <v>3.84</v>
+      </c>
+      <c r="T162">
+        <v>1.44</v>
+      </c>
+      <c r="U162">
+        <v>2.65</v>
+      </c>
+      <c r="V162">
+        <v>2.99</v>
+      </c>
+      <c r="W162">
+        <v>1.36</v>
+      </c>
+      <c r="X162">
+        <v>7.3</v>
+      </c>
+      <c r="Y162">
+        <v>1.07</v>
+      </c>
+      <c r="Z162">
+        <v>2.2</v>
+      </c>
+      <c r="AA162">
+        <v>3.1</v>
+      </c>
+      <c r="AB162">
+        <v>3.1</v>
+      </c>
+      <c r="AC162">
+        <v>1.04</v>
+      </c>
+      <c r="AD162">
+        <v>6.95</v>
+      </c>
+      <c r="AE162">
+        <v>1.33</v>
+      </c>
+      <c r="AF162">
+        <v>2.84</v>
+      </c>
+      <c r="AG162">
+        <v>2</v>
+      </c>
+      <c r="AH162">
+        <v>1.67</v>
+      </c>
+      <c r="AI162">
+        <v>1.83</v>
+      </c>
+      <c r="AJ162">
+        <v>1.87</v>
+      </c>
+      <c r="AK162">
+        <v>1.33</v>
+      </c>
+      <c r="AL162">
+        <v>1.31</v>
+      </c>
+      <c r="AM162">
+        <v>1.63</v>
+      </c>
+      <c r="AN162">
+        <v>2.13</v>
+      </c>
+      <c r="AO162">
+        <v>1.44</v>
+      </c>
+      <c r="AP162">
+        <v>2</v>
+      </c>
+      <c r="AQ162">
+        <v>1.4</v>
+      </c>
+      <c r="AR162">
+        <v>1.69</v>
+      </c>
+      <c r="AS162">
+        <v>1.44</v>
+      </c>
+      <c r="AT162">
+        <v>3.13</v>
+      </c>
+      <c r="AU162">
+        <v>2</v>
+      </c>
+      <c r="AV162">
+        <v>0</v>
+      </c>
+      <c r="AW162">
+        <v>5</v>
+      </c>
+      <c r="AX162">
+        <v>6</v>
+      </c>
+      <c r="AY162">
+        <v>7</v>
+      </c>
+      <c r="AZ162">
+        <v>6</v>
+      </c>
+      <c r="BA162">
+        <v>-1</v>
+      </c>
+      <c r="BB162">
+        <v>-1</v>
+      </c>
+      <c r="BC162">
+        <v>-1</v>
+      </c>
+      <c r="BD162">
+        <v>2.13</v>
+      </c>
+      <c r="BE162">
+        <v>6.55</v>
+      </c>
+      <c r="BF162">
+        <v>2.07</v>
+      </c>
+      <c r="BG162">
+        <v>1.15</v>
+      </c>
+      <c r="BH162">
+        <v>4.25</v>
+      </c>
+      <c r="BI162">
+        <v>1.31</v>
+      </c>
+      <c r="BJ162">
+        <v>2.92</v>
+      </c>
+      <c r="BK162">
+        <v>1.58</v>
+      </c>
+      <c r="BL162">
+        <v>2.17</v>
+      </c>
+      <c r="BM162">
+        <v>1.99</v>
+      </c>
+      <c r="BN162">
+        <v>1.73</v>
+      </c>
+      <c r="BO162">
+        <v>2.57</v>
+      </c>
+      <c r="BP162">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="282">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -598,6 +598,9 @@
     <t>['45', '83']</t>
   </si>
   <si>
+    <t>['13', '64']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -854,6 +857,9 @@
   </si>
   <si>
     <t>['90']</t>
+  </si>
+  <si>
+    <t>['52', '84']</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1471,7 +1477,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1677,7 +1683,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1883,7 +1889,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2295,7 +2301,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2501,7 +2507,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2913,7 +2919,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3325,7 +3331,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3609,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ12">
         <v>0.67</v>
@@ -3737,7 +3743,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3943,7 +3949,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4149,7 +4155,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4355,7 +4361,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4436,7 +4442,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ16">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4973,7 +4979,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5179,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5797,7 +5803,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6209,7 +6215,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6621,7 +6627,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7033,7 +7039,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7239,7 +7245,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7317,7 +7323,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ30">
         <v>0.5600000000000001</v>
@@ -7651,7 +7657,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8063,7 +8069,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8269,7 +8275,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8350,7 +8356,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ35">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR35">
         <v>1.95</v>
@@ -8475,7 +8481,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8887,7 +8893,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9093,7 +9099,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9505,7 +9511,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9711,7 +9717,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10123,7 +10129,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10329,7 +10335,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10741,7 +10747,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10947,7 +10953,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11153,7 +11159,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11234,7 +11240,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ49">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR49">
         <v>1.23</v>
@@ -11359,7 +11365,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11565,7 +11571,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11849,7 +11855,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ52">
         <v>0.88</v>
@@ -12183,7 +12189,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12595,7 +12601,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12801,7 +12807,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13213,7 +13219,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13291,7 +13297,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ59">
         <v>1.25</v>
@@ -14449,7 +14455,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14861,7 +14867,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -14942,7 +14948,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ67">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR67">
         <v>1.38</v>
@@ -15067,7 +15073,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16097,7 +16103,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16303,7 +16309,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16381,7 +16387,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ74">
         <v>1.56</v>
@@ -16509,7 +16515,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16715,7 +16721,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17127,7 +17133,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17539,7 +17545,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -18157,7 +18163,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18238,7 +18244,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ83">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR83">
         <v>1.45</v>
@@ -18775,7 +18781,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19187,7 +19193,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19599,7 +19605,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19805,7 +19811,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20011,7 +20017,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20089,7 +20095,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ92">
         <v>1.33</v>
@@ -20217,7 +20223,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20423,7 +20429,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20629,7 +20635,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21041,7 +21047,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21247,7 +21253,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21453,7 +21459,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22277,7 +22283,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22689,7 +22695,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22895,7 +22901,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23101,7 +23107,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23307,7 +23313,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23513,7 +23519,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24006,7 +24012,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ111">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24337,7 +24343,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24543,7 +24549,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24955,7 +24961,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25033,7 +25039,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ116">
         <v>1.33</v>
@@ -25161,7 +25167,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25367,7 +25373,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26191,7 +26197,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26603,7 +26609,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27015,7 +27021,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27427,7 +27433,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27839,7 +27845,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28251,7 +28257,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28457,7 +28463,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28663,7 +28669,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28741,7 +28747,7 @@
         <v>1.43</v>
       </c>
       <c r="AP134">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ134">
         <v>1.6</v>
@@ -28950,7 +28956,7 @@
         <v>2</v>
       </c>
       <c r="AQ135">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR135">
         <v>1.3</v>
@@ -29281,7 +29287,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29693,7 +29699,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30105,7 +30111,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30186,7 +30192,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ141">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30517,7 +30523,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30723,7 +30729,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30801,7 +30807,7 @@
         <v>1.29</v>
       </c>
       <c r="AP144">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ144">
         <v>1.33</v>
@@ -31135,7 +31141,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31341,7 +31347,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31547,7 +31553,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32165,7 +32171,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32371,7 +32377,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32577,7 +32583,7 @@
         <v>140</v>
       </c>
       <c r="P153" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q153">
         <v>2.96</v>
@@ -32783,7 +32789,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33607,7 +33613,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34225,7 +34231,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34336,13 +34342,13 @@
         <v>16</v>
       </c>
       <c r="BA161">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB161">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BC161">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD161">
         <v>1.75</v>
@@ -34542,13 +34548,13 @@
         <v>6</v>
       </c>
       <c r="BA162">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB162">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC162">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD162">
         <v>2.13</v>
@@ -34588,6 +34594,212 @@
       </c>
       <c r="BP162">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7502759</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45677.625</v>
+      </c>
+      <c r="F163">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>80</v>
+      </c>
+      <c r="H163" t="s">
+        <v>74</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>2</v>
+      </c>
+      <c r="M163">
+        <v>2</v>
+      </c>
+      <c r="N163">
+        <v>4</v>
+      </c>
+      <c r="O163" t="s">
+        <v>194</v>
+      </c>
+      <c r="P163" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q163">
+        <v>4.2</v>
+      </c>
+      <c r="R163">
+        <v>2</v>
+      </c>
+      <c r="S163">
+        <v>2.7</v>
+      </c>
+      <c r="T163">
+        <v>1.45</v>
+      </c>
+      <c r="U163">
+        <v>2.55</v>
+      </c>
+      <c r="V163">
+        <v>2.95</v>
+      </c>
+      <c r="W163">
+        <v>1.35</v>
+      </c>
+      <c r="X163">
+        <v>7.4</v>
+      </c>
+      <c r="Y163">
+        <v>1.06</v>
+      </c>
+      <c r="Z163">
+        <v>4</v>
+      </c>
+      <c r="AA163">
+        <v>3.1</v>
+      </c>
+      <c r="AB163">
+        <v>1.95</v>
+      </c>
+      <c r="AC163">
+        <v>1.02</v>
+      </c>
+      <c r="AD163">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE163">
+        <v>1.33</v>
+      </c>
+      <c r="AF163">
+        <v>3.1</v>
+      </c>
+      <c r="AG163">
+        <v>2.05</v>
+      </c>
+      <c r="AH163">
+        <v>1.8</v>
+      </c>
+      <c r="AI163">
+        <v>1.8</v>
+      </c>
+      <c r="AJ163">
+        <v>1.95</v>
+      </c>
+      <c r="AK163">
+        <v>1.75</v>
+      </c>
+      <c r="AL163">
+        <v>1.28</v>
+      </c>
+      <c r="AM163">
+        <v>1.25</v>
+      </c>
+      <c r="AN163">
+        <v>0.44</v>
+      </c>
+      <c r="AO163">
+        <v>2.38</v>
+      </c>
+      <c r="AP163">
+        <v>0.5</v>
+      </c>
+      <c r="AQ163">
+        <v>2.22</v>
+      </c>
+      <c r="AR163">
+        <v>1.12</v>
+      </c>
+      <c r="AS163">
+        <v>1.31</v>
+      </c>
+      <c r="AT163">
+        <v>2.43</v>
+      </c>
+      <c r="AU163">
+        <v>8</v>
+      </c>
+      <c r="AV163">
+        <v>7</v>
+      </c>
+      <c r="AW163">
+        <v>10</v>
+      </c>
+      <c r="AX163">
+        <v>10</v>
+      </c>
+      <c r="AY163">
+        <v>18</v>
+      </c>
+      <c r="AZ163">
+        <v>17</v>
+      </c>
+      <c r="BA163">
+        <v>10</v>
+      </c>
+      <c r="BB163">
+        <v>9</v>
+      </c>
+      <c r="BC163">
+        <v>19</v>
+      </c>
+      <c r="BD163">
+        <v>2.04</v>
+      </c>
+      <c r="BE163">
+        <v>6.65</v>
+      </c>
+      <c r="BF163">
+        <v>2.15</v>
+      </c>
+      <c r="BG163">
+        <v>1.1</v>
+      </c>
+      <c r="BH163">
+        <v>5.15</v>
+      </c>
+      <c r="BI163">
+        <v>1.23</v>
+      </c>
+      <c r="BJ163">
+        <v>3.42</v>
+      </c>
+      <c r="BK163">
+        <v>1.44</v>
+      </c>
+      <c r="BL163">
+        <v>2.51</v>
+      </c>
+      <c r="BM163">
+        <v>1.76</v>
+      </c>
+      <c r="BN163">
+        <v>1.95</v>
+      </c>
+      <c r="BO163">
+        <v>2.19</v>
+      </c>
+      <c r="BP163">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="283">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -599,6 +599,9 @@
   </si>
   <si>
     <t>['13', '64']</t>
+  </si>
+  <si>
+    <t>['16', '78']</t>
   </si>
   <si>
     <t>['24', '27']</t>
@@ -1221,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1477,7 +1480,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1683,7 +1686,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1889,7 +1892,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2173,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ5">
         <v>1.56</v>
@@ -2301,7 +2304,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2507,7 +2510,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2588,7 +2591,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2919,7 +2922,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3331,7 +3334,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3743,7 +3746,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3949,7 +3952,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4155,7 +4158,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4361,7 +4364,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4979,7 +4982,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5185,7 +5188,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5472,7 +5475,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ21">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR21">
         <v>1.84</v>
@@ -5803,7 +5806,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6087,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ24">
         <v>0.3</v>
@@ -6215,7 +6218,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6627,7 +6630,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7039,7 +7042,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7245,7 +7248,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7657,7 +7660,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8069,7 +8072,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8275,7 +8278,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8481,7 +8484,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8893,7 +8896,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9099,7 +9102,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9383,7 +9386,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ40">
         <v>1.6</v>
@@ -9511,7 +9514,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9717,7 +9720,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10129,7 +10132,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10335,7 +10338,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10747,7 +10750,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10953,7 +10956,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11159,7 +11162,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11365,7 +11368,7 @@
         <v>121</v>
       </c>
       <c r="P50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11571,7 +11574,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11858,7 +11861,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ52">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -12189,7 +12192,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12601,7 +12604,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12807,7 +12810,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13219,7 +13222,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14455,7 +14458,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14867,7 +14870,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15073,7 +15076,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15151,7 +15154,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ68">
         <v>1.4</v>
@@ -15566,7 +15569,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ70">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR70">
         <v>1.47</v>
@@ -16103,7 +16106,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16309,7 +16312,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16515,7 +16518,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16721,7 +16724,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17133,7 +17136,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17545,7 +17548,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17832,7 +17835,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ81">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18163,7 +18166,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18653,7 +18656,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ85">
         <v>1.5</v>
@@ -18781,7 +18784,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19193,7 +19196,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19605,7 +19608,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19811,7 +19814,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20017,7 +20020,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20223,7 +20226,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20429,7 +20432,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20635,7 +20638,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21047,7 +21050,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21253,7 +21256,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21459,7 +21462,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22155,7 +22158,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ102">
         <v>0.5600000000000001</v>
@@ -22283,7 +22286,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22570,7 +22573,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ104">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR104">
         <v>1.44</v>
@@ -22695,7 +22698,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22901,7 +22904,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23107,7 +23110,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23313,7 +23316,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23519,7 +23522,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24343,7 +24346,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24549,7 +24552,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24961,7 +24964,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25167,7 +25170,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25373,7 +25376,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26197,7 +26200,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26609,7 +26612,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27021,7 +27024,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27308,7 +27311,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ127">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR127">
         <v>0.99</v>
@@ -27433,7 +27436,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27511,7 +27514,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ128">
         <v>0.63</v>
@@ -27845,7 +27848,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28257,7 +28260,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28463,7 +28466,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28669,7 +28672,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29287,7 +29290,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29574,7 +29577,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -29699,7 +29702,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30111,7 +30114,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30523,7 +30526,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30729,7 +30732,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31141,7 +31144,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31347,7 +31350,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31553,7 +31556,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31837,7 +31840,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ149">
         <v>1.11</v>
@@ -32171,7 +32174,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32377,7 +32380,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32583,7 +32586,7 @@
         <v>140</v>
       </c>
       <c r="P153" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q153">
         <v>2.96</v>
@@ -32789,7 +32792,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33613,7 +33616,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34231,7 +34234,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34643,7 +34646,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34800,6 +34803,212 @@
       </c>
       <c r="BP163">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7502774</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45681.625</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>73</v>
+      </c>
+      <c r="H164" t="s">
+        <v>83</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>2</v>
+      </c>
+      <c r="L164">
+        <v>2</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>3</v>
+      </c>
+      <c r="O164" t="s">
+        <v>195</v>
+      </c>
+      <c r="P164" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q164">
+        <v>2.55</v>
+      </c>
+      <c r="R164">
+        <v>2</v>
+      </c>
+      <c r="S164">
+        <v>4.5</v>
+      </c>
+      <c r="T164">
+        <v>1.47</v>
+      </c>
+      <c r="U164">
+        <v>2.5</v>
+      </c>
+      <c r="V164">
+        <v>3.25</v>
+      </c>
+      <c r="W164">
+        <v>1.3</v>
+      </c>
+      <c r="X164">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="Y164">
+        <v>1.04</v>
+      </c>
+      <c r="Z164">
+        <v>1.91</v>
+      </c>
+      <c r="AA164">
+        <v>3.2</v>
+      </c>
+      <c r="AB164">
+        <v>3.6</v>
+      </c>
+      <c r="AC164">
+        <v>1.03</v>
+      </c>
+      <c r="AD164">
+        <v>7.2</v>
+      </c>
+      <c r="AE164">
+        <v>1.4</v>
+      </c>
+      <c r="AF164">
+        <v>2.8</v>
+      </c>
+      <c r="AG164">
+        <v>2.2</v>
+      </c>
+      <c r="AH164">
+        <v>1.6</v>
+      </c>
+      <c r="AI164">
+        <v>2</v>
+      </c>
+      <c r="AJ164">
+        <v>1.75</v>
+      </c>
+      <c r="AK164">
+        <v>1.18</v>
+      </c>
+      <c r="AL164">
+        <v>1.25</v>
+      </c>
+      <c r="AM164">
+        <v>1.85</v>
+      </c>
+      <c r="AN164">
+        <v>1.75</v>
+      </c>
+      <c r="AO164">
+        <v>0.88</v>
+      </c>
+      <c r="AP164">
+        <v>1.89</v>
+      </c>
+      <c r="AQ164">
+        <v>0.78</v>
+      </c>
+      <c r="AR164">
+        <v>1.48</v>
+      </c>
+      <c r="AS164">
+        <v>1.36</v>
+      </c>
+      <c r="AT164">
+        <v>2.84</v>
+      </c>
+      <c r="AU164">
+        <v>2</v>
+      </c>
+      <c r="AV164">
+        <v>3</v>
+      </c>
+      <c r="AW164">
+        <v>8</v>
+      </c>
+      <c r="AX164">
+        <v>8</v>
+      </c>
+      <c r="AY164">
+        <v>10</v>
+      </c>
+      <c r="AZ164">
+        <v>11</v>
+      </c>
+      <c r="BA164">
+        <v>2</v>
+      </c>
+      <c r="BB164">
+        <v>7</v>
+      </c>
+      <c r="BC164">
+        <v>9</v>
+      </c>
+      <c r="BD164">
+        <v>1.64</v>
+      </c>
+      <c r="BE164">
+        <v>8.5</v>
+      </c>
+      <c r="BF164">
+        <v>2.66</v>
+      </c>
+      <c r="BG164">
+        <v>1.23</v>
+      </c>
+      <c r="BH164">
+        <v>3.92</v>
+      </c>
+      <c r="BI164">
+        <v>1.42</v>
+      </c>
+      <c r="BJ164">
+        <v>2.73</v>
+      </c>
+      <c r="BK164">
+        <v>1.69</v>
+      </c>
+      <c r="BL164">
+        <v>2.09</v>
+      </c>
+      <c r="BM164">
+        <v>2.11</v>
+      </c>
+      <c r="BN164">
+        <v>1.68</v>
+      </c>
+      <c r="BO164">
+        <v>2.72</v>
+      </c>
+      <c r="BP164">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>
